--- a/tools/excel/3xlsx/currency.xlsx
+++ b/tools/excel/3xlsx/currency.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,29 +536,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>体力</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>UI/Currency/diamond</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>体力</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
         <is>
           <t>UI/Currency/energy</t>
         </is>
